--- a/Applied_Research_Framework_Git/Applied_research/Factor_investing_research/Factor_investing_data.xlsx
+++ b/Applied_Research_Framework_Git/Applied_research/Factor_investing_research/Factor_investing_data.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ueve-my.sharepoint.com/personal/20230348_etud_univ-evry_fr/Documents/Google Drive/Mon Drive/Research/Research articles/Smart Beta &amp; Covid-19/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ueve-my.sharepoint.com/personal/20230348_etud_univ-evry_fr/Documents/Google Drive/Mon Drive/Research/Smart Beta &amp; Covid-19/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{EB1F5D1A-D29C-9441-B77C-F7E998A8DDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E927B082-17A6-1A4D-9473-BAD0BF92D4F4}"/>
+    <workbookView xWindow="4720" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E927B082-17A6-1A4D-9473-BAD0BF92D4F4}"/>
   </bookViews>
   <sheets>
     <sheet name="data_factors" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="chartTableData">#REF!</definedName>
     <definedName name="chartTableHeader">#REF!</definedName>
@@ -185,52 +182,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Presentation"/>
-      <sheetName val="Strategy analysis"/>
-      <sheetName val="VIX index"/>
-      <sheetName val="10y US bond FRED Graph"/>
-      <sheetName val="COVID Data"/>
-      <sheetName val="SPX_data"/>
-      <sheetName val="Global_data"/>
-      <sheetName val="Ranking of Factor styles"/>
-      <sheetName val="Momentum"/>
-      <sheetName val="Min Vol"/>
-      <sheetName val="Quality"/>
-      <sheetName val="Value"/>
-      <sheetName val="Multifactor"/>
-      <sheetName val="Size factor"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -268,7 +223,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -374,7 +329,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -516,7 +471,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
